--- a/Publicgriveance/complaints.xlsx
+++ b/Publicgriveance/complaints.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,6 +802,112 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Drainage Clean</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Need to clean</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-06-17 06:25:08</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Kondalampatty Zone-IV</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Venkat</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kumar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes, need to be cleaned</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>--Select--</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>--Select--</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Madhi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Publicgriveance/complaints.xlsx
+++ b/Publicgriveance/complaints.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,489 +424,209 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>complaint_no</t>
+          <t>complaint_attender</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>citizen_name</t>
+          <t>complaint_date</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>zonal_office</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>petitioner_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>mobile</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>petitioner_address</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>ward_no</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>village</t>
-        </is>
-      </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>ward_notification_status</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>ward_representative</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>response_details</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>remarks</t>
+          <t>informed_to_department</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>followup_date</t>
+          <t>inital_action_status</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>division_no</t>
+          <t>progress_update_status</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>zonal_office</t>
+          <t>final_resolution_status</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>complaint_attender</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>complaint_date</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>ward_notification_status</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>ward_representative</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>representative</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>response_details</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>informed_to_department</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>inital_action_status</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>progress_update_status</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>final_resolution_status</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>petitioner_address</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
           <t>remarks_and_notes</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>petitioner_name</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>raj</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kondalampatty Zone-IV</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Venkat</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>8122529</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>New Road</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-06-16 22:06:43</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>--Select--</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>--Select--</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>--Select--</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>--Select--</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Muthu</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>--Select--</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>--Select--</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>--Select--</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>--Select--</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Venkat</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>kumar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>--Select--</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>kk</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>New Road</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-06-16 22:07:09</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>--Select--</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>--Select--</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>--Select--</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>--Select--</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>asda</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>asaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>New Road</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-06-16 22:07:27</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>--Select--</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>asdaa</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Informed</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>asaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>999999999</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Drainage Clean</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Need to clean</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-17 06:25:08</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Kondalampatty Zone-IV</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Venkat</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Kumar</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Yes, need to be cleaned</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>--Select--</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>--Select--</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Salem</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Madhi</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
